--- a/excel-files/PARANAQUE/SUN VALLEY NATIONAL HIGH SCHOOL.xlsx
+++ b/excel-files/PARANAQUE/SUN VALLEY NATIONAL HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{809D7682-1916-4AF9-8E69-F07EC0A293CB}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8823E2F4-6050-49CB-8723-21E62EA2C003}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -229,6 +229,9 @@
     <t>MAPEH</t>
   </si>
   <si>
+    <t>RO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quantity based on Target ADM-SLM - Q1 </t>
   </si>
   <si>
@@ -311,9 +314,6 @@
   </si>
   <si>
     <t>Arts</t>
-  </si>
-  <si>
-    <t>RO</t>
   </si>
 </sst>
 </file>
@@ -5475,8 +5475,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5491,7 +5491,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -10022,7 +10022,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10034,16 +10034,22 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E73" s="12"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="12"/>
+      <c r="E73" s="12">
+        <v>87</v>
+      </c>
+      <c r="F73" s="10">
+        <v>2025</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="H73" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I73" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J73" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -10091,7 +10097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10103,16 +10109,22 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E74" s="12"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="12"/>
+      <c r="E74" s="12">
+        <v>87</v>
+      </c>
+      <c r="F74" s="10">
+        <v>2025</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="H74" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I74" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J74" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -10160,7 +10172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10172,16 +10184,22 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E75" s="12"/>
-      <c r="F75" s="10"/>
-      <c r="G75" s="12"/>
+      <c r="E75" s="12">
+        <v>87</v>
+      </c>
+      <c r="F75" s="10">
+        <v>2025</v>
+      </c>
+      <c r="G75" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="H75" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I75" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J75" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -10229,7 +10247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10241,16 +10259,22 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E76" s="12"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="12"/>
+      <c r="E76" s="12">
+        <v>87</v>
+      </c>
+      <c r="F76" s="10">
+        <v>2025</v>
+      </c>
+      <c r="G76" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="H76" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I76" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J76" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -10298,7 +10322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10310,16 +10334,22 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E77" s="12"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="12"/>
+      <c r="E77" s="12">
+        <v>87</v>
+      </c>
+      <c r="F77" s="10">
+        <v>2025</v>
+      </c>
+      <c r="G77" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="H77" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I77" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J77" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -10367,7 +10397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="19.5">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10379,16 +10409,22 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E78" s="12"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="12"/>
+      <c r="E78" s="12">
+        <v>87</v>
+      </c>
+      <c r="F78" s="10">
+        <v>2025</v>
+      </c>
+      <c r="G78" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="H78" s="12">
         <f t="shared" ref="H78:H127" si="22">IF((D78-E78)&lt;0,0,(D78-E78))</f>
         <v>0</v>
       </c>
       <c r="I78" s="12">
         <f t="shared" ref="I78:I127" si="23">IF((E78-D78)&lt;0,0,(E78-D78))</f>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J78" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -10436,7 +10472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10448,16 +10484,22 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E79" s="12"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="12"/>
+      <c r="E79" s="12">
+        <v>87</v>
+      </c>
+      <c r="F79" s="10">
+        <v>2025</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="H79" s="12">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I79" s="12">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J79" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -10505,7 +10547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10517,16 +10559,22 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E80" s="12"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="12"/>
+      <c r="E80" s="12">
+        <v>87</v>
+      </c>
+      <c r="F80" s="10">
+        <v>2025</v>
+      </c>
+      <c r="G80" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="H80" s="12">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I80" s="12">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J80" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -10574,7 +10622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10586,16 +10634,22 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E81" s="12"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="12"/>
+      <c r="E81" s="12">
+        <v>87</v>
+      </c>
+      <c r="F81" s="10">
+        <v>2025</v>
+      </c>
+      <c r="G81" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="H81" s="12">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I81" s="12">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J81" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -13420,7 +13474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13479,191 +13533,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D73:F81" name="LAS"/>
+    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G83:G91 G93:G101 G103:G110 G73:G81" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -13676,10 +13550,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G103:G110 G83:G91 G93:G101 G73:G81" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13695,7 +13569,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13769,76 +13643,76 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M2" s="43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N2" s="43" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O2" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y2" s="44" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z2" s="44" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AA2" s="26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="19.149999999999999">
@@ -15988,7 +15862,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5">
@@ -16057,7 +15931,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -16195,7 +16069,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5">
@@ -16264,7 +16138,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="5">
@@ -16748,7 +16622,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5">
@@ -16817,7 +16691,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="5">
@@ -16955,7 +16829,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5">
@@ -17024,7 +16898,7 @@
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -17508,7 +17382,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5">
@@ -17577,7 +17451,7 @@
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="5">
@@ -17715,7 +17589,7 @@
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5">
@@ -17784,7 +17658,7 @@
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="5">
@@ -17971,7 +17845,7 @@
         <v>2025</v>
       </c>
       <c r="S68" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T68" s="12">
         <f t="shared" si="4"/>
@@ -18286,7 +18160,7 @@
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C73" s="10">
         <v>590</v>
@@ -18357,7 +18231,7 @@
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C74" s="10">
         <v>590</v>
@@ -18499,7 +18373,7 @@
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C76" s="10">
         <v>590</v>
@@ -18570,7 +18444,7 @@
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C77" s="10">
         <v>590</v>
@@ -18759,7 +18633,7 @@
         <v>2025</v>
       </c>
       <c r="S80" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T80" s="12">
         <f t="shared" si="16"/>
@@ -18836,7 +18710,7 @@
         <v>2025</v>
       </c>
       <c r="S81" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T81" s="12">
         <f t="shared" si="16"/>
@@ -19080,7 +18954,7 @@
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C85" s="10">
         <v>570</v>
@@ -19151,7 +19025,7 @@
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C86" s="10">
         <v>570</v>
@@ -19293,7 +19167,7 @@
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C88" s="10">
         <v>570</v>
@@ -19364,7 +19238,7 @@
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C89" s="10">
         <v>570</v>
@@ -19542,7 +19416,7 @@
         <v>2025</v>
       </c>
       <c r="M92" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="N92" s="12">
         <f t="shared" si="20"/>
@@ -19627,7 +19501,7 @@
         <v>2025</v>
       </c>
       <c r="M93" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="N93" s="12">
         <f t="shared" si="20"/>
@@ -19918,7 +19792,7 @@
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C97" s="10">
         <v>571</v>
@@ -19993,7 +19867,7 @@
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C98" s="10">
         <v>571</v>
@@ -20139,7 +20013,7 @@
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C100" s="10">
         <v>571</v>
@@ -20218,7 +20092,7 @@
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C101" s="10">
         <v>571</v>
@@ -20329,7 +20203,7 @@
         <v>2025</v>
       </c>
       <c r="M103" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="N103" s="12">
         <f t="shared" si="20"/>
@@ -20350,7 +20224,7 @@
         <v>2025</v>
       </c>
       <c r="S103" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T103" s="12">
         <f t="shared" si="16"/>
@@ -20371,7 +20245,7 @@
         <v>2025</v>
       </c>
       <c r="Y103" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z103" s="12">
         <f t="shared" si="18"/>
@@ -20448,7 +20322,7 @@
         <v>2025</v>
       </c>
       <c r="Y104" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z104" s="12">
         <f t="shared" si="18"/>
@@ -20495,7 +20369,7 @@
         <v>2025</v>
       </c>
       <c r="M105" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="N105" s="12">
         <f t="shared" si="20"/>
@@ -20516,7 +20390,7 @@
         <v>2025</v>
       </c>
       <c r="S105" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T105" s="12">
         <f t="shared" si="16"/>
@@ -20537,7 +20411,7 @@
         <v>2025</v>
       </c>
       <c r="Y105" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z105" s="12">
         <f t="shared" si="18"/>
@@ -20614,7 +20488,7 @@
         <v>2025</v>
       </c>
       <c r="Y106" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z106" s="12">
         <f t="shared" si="18"/>
@@ -20691,7 +20565,7 @@
         <v>2025</v>
       </c>
       <c r="Y107" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z107" s="12">
         <f t="shared" si="18"/>
@@ -20768,7 +20642,7 @@
         <v>2025</v>
       </c>
       <c r="Y108" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z108" s="12">
         <f t="shared" si="18"/>
@@ -20784,7 +20658,7 @@
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C109" s="10">
         <v>517</v>
@@ -20845,7 +20719,7 @@
         <v>2025</v>
       </c>
       <c r="Y109" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z109" s="12">
         <f>IF((V109-W109)&lt;0,0,(V109-W109))</f>
@@ -20861,7 +20735,7 @@
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C110" s="10">
         <v>517</v>
@@ -20922,7 +20796,7 @@
         <v>2025</v>
       </c>
       <c r="Y110" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z110" s="12">
         <f t="shared" si="18"/>
@@ -21009,7 +20883,7 @@
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C112" s="10">
         <v>517</v>
@@ -21070,7 +20944,7 @@
         <v>2025</v>
       </c>
       <c r="Y112" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z112" s="12">
         <f>IF((V112-W112)&lt;0,0,(V112-W112))</f>
@@ -21086,7 +20960,7 @@
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C113" s="10">
         <v>517</v>
@@ -21147,7 +21021,7 @@
         <v>2025</v>
       </c>
       <c r="Y113" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z113" s="12">
         <f t="shared" si="18"/>
@@ -22238,186 +22112,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C115:C122 C103:C113 C91:C101 C79:C89 C67:C77" name="Textbooks"/>
@@ -22437,8 +22131,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 M115:M122 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M103:M113 G91:G101 G103:G113 Y103:Y113 S103:S113 S79:S89 M91:M101" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 F103:F113 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L103:L113 R91:R101 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 X91:X101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 L91:L101" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
